--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -674,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -751,7 +766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -828,7 +843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -905,7 +920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -982,7 +997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1059,7 +1074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1136,7 +1151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1213,7 +1228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1290,7 +1305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1367,7 +1382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1444,7 +1459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1521,7 +1536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1598,7 +1613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1675,7 +1690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1752,7 +1767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1829,7 +1844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1906,7 +1921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1983,7 +1998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2060,7 +2075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2137,7 +2152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2214,7 +2229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2291,7 +2306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2368,7 +2383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2445,7 +2460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2522,7 +2537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2599,7 +2614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2676,7 +2691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2753,7 +2768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2830,7 +2845,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2907,7 +2922,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2984,7 +2999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3017,7 +3032,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="8" t="n">
         <v>12.9397883043262</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -3063,7 +3078,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3096,7 +3111,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="8" t="n">
         <v>12.1130825063316</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3142,7 +3157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3175,7 +3190,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="8" t="n">
         <v>11.6034920164865</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -3221,7 +3236,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3254,7 +3269,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="8" t="n">
         <v>14.2846874680057</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3300,7 +3315,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3333,7 +3348,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="8" t="n">
         <v>13.8975744531453</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -3379,7 +3394,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3412,7 +3427,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="8" t="n">
         <v>13.9142872164206</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -3458,7 +3473,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3491,7 +3506,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="8" t="n">
         <v>11.1393296925068</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3537,7 +3552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3570,7 +3585,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="8" t="n">
         <v>10.2902818879867</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3616,7 +3631,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3649,7 +3664,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N46" s="8" t="n">
         <v>10.5018322840826</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3695,7 +3710,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3728,7 +3743,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="8" t="n">
         <v>10.9389737028272</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3774,7 +3789,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3807,7 +3822,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N48" s="8" t="n">
         <v>9.958015480089029</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -3853,7 +3868,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3886,7 +3901,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="8" t="n">
         <v>10.2838550220653</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -3932,7 +3947,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3965,7 +3980,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="8" t="n">
         <v>11.0969592479254</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
@@ -4011,7 +4026,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4044,7 +4059,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="8" t="n">
         <v>10.8221115135209</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4090,7 +4105,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4123,7 +4138,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="8" t="n">
         <v>10.285304207933</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
@@ -4169,7 +4184,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4202,7 +4217,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="8" t="n">
         <v>9.417589050741711</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4248,7 +4263,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4281,7 +4296,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N54" s="8" t="n">
         <v>8.836544594309821</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
@@ -4327,7 +4342,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4360,7 +4375,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="8" t="n">
         <v>8.51775190146885</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4406,7 +4421,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4439,7 +4454,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N56" s="8" t="n">
         <v>8.62966029399127</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4485,7 +4500,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4518,7 +4533,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="8" t="n">
         <v>8.54502980363339</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -4564,7 +4579,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4597,7 +4612,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N58" s="8" t="n">
         <v>8.052488855112861</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
@@ -4643,7 +4658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4676,7 +4691,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="8" t="n">
         <v>7.74338803787381</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -4722,7 +4737,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4755,7 +4770,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="8" t="n">
         <v>7.44570387746484</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
@@ -4801,7 +4816,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4834,7 +4849,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="8" t="n">
         <v>6.83822683797926</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -4880,7 +4895,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4913,7 +4928,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N62" s="8" t="n">
         <v>6.44996892704785</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
@@ -4959,7 +4974,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4992,7 +5007,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="N63" s="8" t="n">
         <v>6.05440848477047</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -5038,7 +5053,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5071,7 +5086,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="N64" s="8" t="n">
         <v>8.08683421779959</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5117,7 +5132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5150,7 +5165,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="8" t="n">
         <v>8.79253921551871</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5196,7 +5211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5229,7 +5244,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="8" t="n">
         <v>9.179744714338851</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
@@ -5275,7 +5290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5308,7 +5323,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="8" t="n">
         <v>9.78335796574615</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -5354,7 +5369,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5387,7 +5402,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="8" t="n">
         <v>9.77794667025743</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5433,7 +5448,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5466,7 +5481,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
+      <c r="N69" s="8" t="n">
         <v>9.405118056478569</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -5512,7 +5527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5545,7 +5560,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="8" t="n">
         <v>9.180922027364741</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
@@ -5591,7 +5606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5624,7 +5639,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="8" t="n">
         <v>8.90218335115606</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -5670,7 +5685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5703,7 +5718,7 @@
           <t>Empleo en agricultura como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
+      <c r="N72" s="8" t="n">
         <v>8.87472626253569</v>
       </c>
       <c r="O72" s="4" t="inlineStr">
@@ -5749,7 +5764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5826,7 +5841,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -5903,7 +5918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -5980,7 +5995,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6057,7 +6072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6134,7 +6149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6211,7 +6226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6288,7 +6303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6365,7 +6380,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6442,7 +6457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6519,7 +6534,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6596,7 +6611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6673,7 +6688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6750,7 +6765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -6827,7 +6842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6904,7 +6919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6981,7 +6996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7058,7 +7073,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7135,7 +7150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7212,7 +7227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7289,7 +7304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7366,7 +7381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7443,7 +7458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7520,7 +7535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7597,7 +7612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7674,7 +7689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -7751,7 +7766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -7828,7 +7843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -7905,7 +7920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -7982,7 +7997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8059,7 +8074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8136,7 +8151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8169,7 +8184,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N104" s="4" t="n">
+      <c r="N104" s="8" t="n">
         <v>58.426</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
@@ -8215,7 +8230,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8248,7 +8263,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n">
+      <c r="N105" s="8" t="n">
         <v>59.776</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
@@ -8294,7 +8309,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8327,7 +8342,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N106" s="4" t="n">
+      <c r="N106" s="8" t="n">
         <v>60.362</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8373,7 +8388,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8406,7 +8421,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N107" s="4" t="n">
+      <c r="N107" s="8" t="n">
         <v>58.818</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8452,7 +8467,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8485,7 +8500,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N108" s="4" t="n">
+      <c r="N108" s="8" t="n">
         <v>57.843</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
@@ -8531,7 +8546,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8564,7 +8579,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N109" s="4" t="n">
+      <c r="N109" s="8" t="n">
         <v>56.721</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8610,7 +8625,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -8643,7 +8658,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N110" s="4" t="n">
+      <c r="N110" s="8" t="n">
         <v>57.358</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
@@ -8689,7 +8704,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -8722,7 +8737,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N111" s="4" t="n">
+      <c r="N111" s="8" t="n">
         <v>57.264</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
@@ -8768,7 +8783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -8801,7 +8816,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N112" s="4" t="n">
+      <c r="N112" s="8" t="n">
         <v>54.607</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
@@ -8847,7 +8862,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -8880,7 +8895,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N113" s="4" t="n">
+      <c r="N113" s="8" t="n">
         <v>55.057</v>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -8926,7 +8941,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -8959,7 +8974,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N114" s="4" t="n">
+      <c r="N114" s="8" t="n">
         <v>55.757</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -9005,7 +9020,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9038,7 +9053,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N115" s="4" t="n">
+      <c r="N115" s="8" t="n">
         <v>53.076</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -9084,7 +9099,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9117,7 +9132,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N116" s="4" t="n">
+      <c r="N116" s="8" t="n">
         <v>52.044</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
@@ -9163,7 +9178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9196,7 +9211,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N117" s="4" t="n">
+      <c r="N117" s="8" t="n">
         <v>54.102</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -9242,7 +9257,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9275,7 +9290,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N118" s="4" t="n">
+      <c r="N118" s="8" t="n">
         <v>57.422</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -9321,7 +9336,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9354,7 +9369,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N119" s="4" t="n">
+      <c r="N119" s="8" t="n">
         <v>59.278</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -9400,7 +9415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9433,7 +9448,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N120" s="4" t="n">
+      <c r="N120" s="8" t="n">
         <v>59.727</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
@@ -9479,7 +9494,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9512,7 +9527,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N121" s="4" t="n">
+      <c r="N121" s="8" t="n">
         <v>60.279</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
@@ -9558,7 +9573,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9591,7 +9606,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N122" s="4" t="n">
+      <c r="N122" s="8" t="n">
         <v>60.138</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
@@ -9637,7 +9652,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -9670,7 +9685,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n">
+      <c r="N123" s="8" t="n">
         <v>59.312</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
@@ -9716,7 +9731,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -9749,7 +9764,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N124" s="4" t="n">
+      <c r="N124" s="8" t="n">
         <v>59.234</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
@@ -9795,7 +9810,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -9828,7 +9843,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n">
+      <c r="N125" s="8" t="n">
         <v>58.948</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
@@ -9874,7 +9889,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -9907,7 +9922,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n">
+      <c r="N126" s="8" t="n">
         <v>57.913</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -9953,7 +9968,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -9986,7 +10001,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n">
+      <c r="N127" s="8" t="n">
         <v>57.914</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10032,7 +10047,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10065,7 +10080,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N128" s="4" t="n">
+      <c r="N128" s="8" t="n">
         <v>57.885</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
@@ -10111,7 +10126,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10144,7 +10159,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N129" s="4" t="n">
+      <c r="N129" s="8" t="n">
         <v>57.93</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
@@ -10190,7 +10205,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10223,7 +10238,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n">
+      <c r="N130" s="8" t="n">
         <v>56.881</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10269,7 +10284,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10302,7 +10317,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N131" s="4" t="n">
+      <c r="N131" s="8" t="n">
         <v>55.011</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
@@ -10348,7 +10363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10381,7 +10396,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N132" s="4" t="n">
+      <c r="N132" s="8" t="n">
         <v>51.914</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
@@ -10427,7 +10442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10460,7 +10475,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N133" s="4" t="n">
+      <c r="N133" s="8" t="n">
         <v>44.55</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10506,7 +10521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10539,7 +10554,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N134" s="4" t="n">
+      <c r="N134" s="8" t="n">
         <v>45.195</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
@@ -10585,7 +10600,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -10618,7 +10633,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N135" s="4" t="n">
+      <c r="N135" s="8" t="n">
         <v>48.01</v>
       </c>
       <c r="O135" s="4" t="inlineStr">
@@ -10664,7 +10679,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -10697,7 +10712,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N136" s="4" t="n">
+      <c r="N136" s="8" t="n">
         <v>48.589</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
@@ -10743,7 +10758,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -10776,7 +10791,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N137" s="4" t="n">
+      <c r="N137" s="8" t="n">
         <v>49.28</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
@@ -10822,7 +10837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -10855,7 +10870,7 @@
           <t>Relación empleo-población</t>
         </is>
       </c>
-      <c r="N138" s="4" t="n">
+      <c r="N138" s="8" t="n">
         <v>49.171</v>
       </c>
       <c r="O138" s="4" t="inlineStr">
@@ -10901,7 +10916,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -10978,7 +10993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11055,7 +11070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11132,7 +11147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11209,7 +11224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11286,7 +11301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11363,7 +11378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11440,7 +11455,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11517,7 +11532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -11594,7 +11609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -11671,7 +11686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -11748,7 +11763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -11825,7 +11840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -11902,7 +11917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -11979,7 +11994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12056,7 +12071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12133,7 +12148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12210,7 +12225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12287,7 +12302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12364,7 +12379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12441,7 +12456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12518,7 +12533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -12595,7 +12610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -12672,7 +12687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -12749,7 +12764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -12826,7 +12841,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -12903,7 +12918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -12980,7 +12995,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13057,7 +13072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13134,7 +13149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13211,7 +13226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13288,7 +13303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13321,7 +13336,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N170" s="4" t="n">
+      <c r="N170" s="8" t="n">
         <v>26.2982471069215</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
@@ -13367,7 +13382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13400,7 +13415,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N171" s="4" t="n">
+      <c r="N171" s="8" t="n">
         <v>26.8541940198558</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
@@ -13446,7 +13461,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -13479,7 +13494,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N172" s="4" t="n">
+      <c r="N172" s="8" t="n">
         <v>26.4788800747171</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
@@ -13525,7 +13540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -13558,7 +13573,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N173" s="4" t="n">
+      <c r="N173" s="8" t="n">
         <v>23.8115339257483</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
@@ -13604,7 +13619,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -13637,7 +13652,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N174" s="4" t="n">
+      <c r="N174" s="8" t="n">
         <v>23.7402817847384</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
@@ -13683,7 +13698,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -13716,7 +13731,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N175" s="4" t="n">
+      <c r="N175" s="8" t="n">
         <v>22.5557782645448</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
@@ -13762,7 +13777,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -13795,7 +13810,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N176" s="4" t="n">
+      <c r="N176" s="8" t="n">
         <v>24.0716545243611</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
@@ -13841,7 +13856,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -13874,7 +13889,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N177" s="4" t="n">
+      <c r="N177" s="8" t="n">
         <v>24.6969857323003</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
@@ -13920,7 +13935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -13953,7 +13968,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N178" s="4" t="n">
+      <c r="N178" s="8" t="n">
         <v>22.9002472657412</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
@@ -13999,7 +14014,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14032,7 +14047,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N179" s="4" t="n">
+      <c r="N179" s="8" t="n">
         <v>22.9889839292935</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
@@ -14078,7 +14093,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14111,7 +14126,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N180" s="4" t="n">
+      <c r="N180" s="8" t="n">
         <v>22.2485631469406</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
@@ -14157,7 +14172,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14190,7 +14205,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N181" s="4" t="n">
+      <c r="N181" s="8" t="n">
         <v>20.8264449076426</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
@@ -14236,7 +14251,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14269,7 +14284,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N182" s="4" t="n">
+      <c r="N182" s="8" t="n">
         <v>19.9924708756272</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
@@ -14315,7 +14330,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14348,7 +14363,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N183" s="4" t="n">
+      <c r="N183" s="8" t="n">
         <v>20.4630636727823</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
@@ -14394,7 +14409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -14427,7 +14442,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N184" s="4" t="n">
+      <c r="N184" s="8" t="n">
         <v>20.6494359006429</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
@@ -14473,7 +14488,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -14506,7 +14521,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N185" s="4" t="n">
+      <c r="N185" s="8" t="n">
         <v>22.1837874825646</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
@@ -14552,7 +14567,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -14585,7 +14600,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N186" s="4" t="n">
+      <c r="N186" s="8" t="n">
         <v>23.1293994132024</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
@@ -14631,7 +14646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -14664,7 +14679,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N187" s="4" t="n">
+      <c r="N187" s="8" t="n">
         <v>22.8729914448606</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -14710,7 +14725,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14743,7 +14758,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N188" s="4" t="n">
+      <c r="N188" s="8" t="n">
         <v>22.4641943117532</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
@@ -14789,7 +14804,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -14822,7 +14837,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N189" s="4" t="n">
+      <c r="N189" s="8" t="n">
         <v>21.9677409284925</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -14868,7 +14883,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -14901,7 +14916,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N190" s="4" t="n">
+      <c r="N190" s="8" t="n">
         <v>21.7971873569326</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
@@ -14947,7 +14962,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -14980,7 +14995,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N191" s="4" t="n">
+      <c r="N191" s="8" t="n">
         <v>21.2617412983533</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
@@ -15026,7 +15041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15059,7 +15074,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N192" s="4" t="n">
+      <c r="N192" s="8" t="n">
         <v>21.3259307880631</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -15105,7 +15120,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15138,7 +15153,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N193" s="4" t="n">
+      <c r="N193" s="8" t="n">
         <v>21.3454768491602</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -15184,7 +15199,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15217,7 +15232,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N194" s="4" t="n">
+      <c r="N194" s="8" t="n">
         <v>21.3119844799713</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
@@ -15263,7 +15278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15296,7 +15311,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N195" s="4" t="n">
+      <c r="N195" s="8" t="n">
         <v>21.1378092637334</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
@@ -15342,7 +15357,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15375,7 +15390,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N196" s="4" t="n">
+      <c r="N196" s="8" t="n">
         <v>20.0638940937792</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
@@ -15421,7 +15436,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -15454,7 +15469,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N197" s="4" t="n">
+      <c r="N197" s="8" t="n">
         <v>18.6723353186815</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -15500,7 +15515,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -15533,7 +15548,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N198" s="4" t="n">
+      <c r="N198" s="8" t="n">
         <v>17.5673651995346</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
@@ -15579,7 +15594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -15612,7 +15627,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N199" s="4" t="n">
+      <c r="N199" s="8" t="n">
         <v>17.5248973989659</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -15658,7 +15673,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -15691,7 +15706,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N200" s="4" t="n">
+      <c r="N200" s="8" t="n">
         <v>17.6150252734504</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
@@ -15737,7 +15752,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -15770,7 +15785,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n">
+      <c r="N201" s="8" t="n">
         <v>17.5364096639575</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
@@ -15816,7 +15831,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -15849,7 +15864,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N202" s="4" t="n">
+      <c r="N202" s="8" t="n">
         <v>17.3276921466437</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
@@ -15895,7 +15910,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -15928,7 +15943,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N203" s="4" t="n">
+      <c r="N203" s="8" t="n">
         <v>17.2136363618923</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
@@ -15974,7 +15989,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16007,7 +16022,7 @@
           <t>Empleo en industria como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N204" s="4" t="n">
+      <c r="N204" s="8" t="n">
         <v>16.7519824595264</v>
       </c>
       <c r="O204" s="4" t="inlineStr">
@@ -16053,7 +16068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16130,7 +16145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16207,7 +16222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16284,7 +16299,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16361,7 +16376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -16438,7 +16453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -16515,7 +16530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -16592,7 +16607,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -16669,7 +16684,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -16746,7 +16761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -16823,7 +16838,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -16900,7 +16915,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -16977,7 +16992,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17054,7 +17069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17131,7 +17146,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17208,7 +17223,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17285,7 +17300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -17362,7 +17377,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -17439,7 +17454,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -17516,7 +17531,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -17593,7 +17608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -17670,7 +17685,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -17747,7 +17762,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -17824,7 +17839,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -17901,7 +17916,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -17978,7 +17993,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18055,7 +18070,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18132,7 +18147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18209,7 +18224,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18286,7 +18301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -18363,7 +18378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -18440,7 +18455,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -18473,7 +18488,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N236" s="4" t="n">
+      <c r="N236" s="8" t="n">
         <v>60.7619781388363</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
@@ -18519,7 +18534,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -18552,7 +18567,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N237" s="4" t="n">
+      <c r="N237" s="8" t="n">
         <v>61.0327234738127</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
@@ -18598,7 +18613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -18631,7 +18646,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N238" s="4" t="n">
+      <c r="N238" s="8" t="n">
         <v>61.9176402890238</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
@@ -18677,7 +18692,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -18710,7 +18725,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N239" s="4" t="n">
+      <c r="N239" s="8" t="n">
         <v>61.903778606246</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
@@ -18756,7 +18771,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -18789,7 +18804,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n">
+      <c r="N240" s="8" t="n">
         <v>62.3621437621163</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
@@ -18835,7 +18850,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -18868,7 +18883,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n">
+      <c r="N241" s="8" t="n">
         <v>63.5299466330253</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
@@ -18914,7 +18929,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -18947,7 +18962,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N242" s="4" t="n">
+      <c r="N242" s="8" t="n">
         <v>64.7890157831321</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
@@ -18993,7 +19008,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19026,7 +19041,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N243" s="4" t="n">
+      <c r="N243" s="8" t="n">
         <v>65.0127437474018</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
@@ -19072,7 +19087,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19105,7 +19120,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n">
+      <c r="N244" s="8" t="n">
         <v>66.5979204501762</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
@@ -19151,7 +19166,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19184,7 +19199,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N245" s="4" t="n">
+      <c r="N245" s="8" t="n">
         <v>66.07204236787931</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
@@ -19230,7 +19245,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -19263,7 +19278,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N246" s="4" t="n">
+      <c r="N246" s="8" t="n">
         <v>67.7934321836923</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
@@ -19309,7 +19324,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -19342,7 +19357,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N247" s="4" t="n">
+      <c r="N247" s="8" t="n">
         <v>68.88970007029209</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
@@ -19388,7 +19403,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -19421,7 +19436,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N248" s="4" t="n">
+      <c r="N248" s="8" t="n">
         <v>68.9105698764474</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
@@ -19467,7 +19482,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -19500,7 +19515,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N249" s="4" t="n">
+      <c r="N249" s="8" t="n">
         <v>68.71482481369679</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
@@ -19546,7 +19561,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -19579,7 +19594,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N250" s="4" t="n">
+      <c r="N250" s="8" t="n">
         <v>69.0652598914242</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
@@ -19625,7 +19640,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -19658,7 +19673,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N251" s="4" t="n">
+      <c r="N251" s="8" t="n">
         <v>68.39862346669371</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
@@ -19704,7 +19719,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -19737,7 +19752,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N252" s="4" t="n">
+      <c r="N252" s="8" t="n">
         <v>68.03405599248779</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
@@ -19783,7 +19798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -19816,7 +19831,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N253" s="4" t="n">
+      <c r="N253" s="8" t="n">
         <v>68.6092481293891</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
@@ -19862,7 +19877,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -19895,7 +19910,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N254" s="4" t="n">
+      <c r="N254" s="8" t="n">
         <v>68.9061370100757</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
@@ -19941,7 +19956,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -19974,7 +19989,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N255" s="4" t="n">
+      <c r="N255" s="8" t="n">
         <v>69.4872292678741</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
@@ -20020,7 +20035,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20053,7 +20068,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N256" s="4" t="n">
+      <c r="N256" s="8" t="n">
         <v>70.1503155774881</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
@@ -20099,7 +20114,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20132,7 +20147,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N257" s="4" t="n">
+      <c r="N257" s="8" t="n">
         <v>70.9948787727543</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
@@ -20178,7 +20193,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -20211,7 +20226,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N258" s="4" t="n">
+      <c r="N258" s="8" t="n">
         <v>71.228365334472</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
@@ -20257,7 +20272,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -20290,7 +20305,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N259" s="4" t="n">
+      <c r="N259" s="8" t="n">
         <v>71.8162963128606</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
@@ -20336,7 +20351,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -20369,7 +20384,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N260" s="4" t="n">
+      <c r="N260" s="8" t="n">
         <v>72.23805446253949</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
@@ -20415,7 +20430,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -20448,7 +20463,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N261" s="4" t="n">
+      <c r="N261" s="8" t="n">
         <v>72.8077900344325</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
@@ -20494,7 +20509,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -20527,7 +20542,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N262" s="4" t="n">
+      <c r="N262" s="8" t="n">
         <v>71.8492557571158</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
@@ -20573,7 +20588,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -20606,7 +20621,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N263" s="4" t="n">
+      <c r="N263" s="8" t="n">
         <v>72.5351339268112</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
@@ -20652,7 +20667,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -20685,7 +20700,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N264" s="4" t="n">
+      <c r="N264" s="8" t="n">
         <v>73.2528900861266</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
@@ -20731,7 +20746,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -20764,7 +20779,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N265" s="4" t="n">
+      <c r="N265" s="8" t="n">
         <v>72.6917446352879</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
@@ -20810,7 +20825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -20843,7 +20858,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N266" s="4" t="n">
+      <c r="N266" s="8" t="n">
         <v>72.60702805629209</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
@@ -20889,7 +20904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -20922,7 +20937,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N267" s="4" t="n">
+      <c r="N267" s="8" t="n">
         <v>73.0584823640864</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
@@ -20968,7 +20983,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21001,7 +21016,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N268" s="4" t="n">
+      <c r="N268" s="8" t="n">
         <v>73.49137597823881</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
@@ -21047,7 +21062,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21080,7 +21095,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n">
+      <c r="N269" s="8" t="n">
         <v>73.8841898793772</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
@@ -21126,7 +21141,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21159,7 +21174,7 @@
           <t>Empleo en servicios como porcentaje del empleo total</t>
         </is>
       </c>
-      <c r="N270" s="4" t="n">
+      <c r="N270" s="8" t="n">
         <v>74.3732817797608</v>
       </c>
       <c r="O270" s="4" t="inlineStr">
@@ -21205,7 +21220,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -21282,7 +21297,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -21359,7 +21374,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -21436,7 +21451,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -21513,7 +21528,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G275" s="4" t="n">
+      <c r="G275" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -21590,7 +21605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G276" s="4" t="n">
+      <c r="G276" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -21667,7 +21682,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G277" s="4" t="n">
+      <c r="G277" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -21744,7 +21759,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G278" s="4" t="n">
+      <c r="G278" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -21821,7 +21836,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G279" s="4" t="n">
+      <c r="G279" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -21898,7 +21913,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G280" s="4" t="n">
+      <c r="G280" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -21975,7 +21990,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G281" s="4" t="n">
+      <c r="G281" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -22052,7 +22067,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G282" s="4" t="n">
+      <c r="G282" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -22129,7 +22144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G283" s="4" t="n">
+      <c r="G283" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
@@ -22206,7 +22221,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G284" s="4" t="n">
+      <c r="G284" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
@@ -22283,7 +22298,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G285" s="4" t="n">
+      <c r="G285" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
@@ -22360,7 +22375,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G286" s="4" t="n">
+      <c r="G286" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
@@ -22437,7 +22452,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G287" s="4" t="n">
+      <c r="G287" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
@@ -22514,7 +22529,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G288" s="4" t="n">
+      <c r="G288" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
@@ -22591,7 +22606,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G289" s="4" t="n">
+      <c r="G289" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
@@ -22668,7 +22683,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G290" s="4" t="n">
+      <c r="G290" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
@@ -22745,7 +22760,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G291" s="4" t="n">
+      <c r="G291" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
@@ -22822,7 +22837,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G292" s="4" t="n">
+      <c r="G292" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
@@ -22899,7 +22914,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G293" s="4" t="n">
+      <c r="G293" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
@@ -22976,7 +22991,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G294" s="4" t="n">
+      <c r="G294" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
@@ -23053,7 +23068,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G295" s="4" t="n">
+      <c r="G295" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
@@ -23130,7 +23145,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G296" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
@@ -23207,7 +23222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n">
+      <c r="G297" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
@@ -23284,7 +23299,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G298" s="4" t="n">
+      <c r="G298" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
@@ -23361,7 +23376,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G299" s="4" t="n">
+      <c r="G299" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -23438,7 +23453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G300" s="4" t="n">
+      <c r="G300" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -23515,7 +23530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G301" s="4" t="n">
+      <c r="G301" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -23548,7 +23563,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N301" s="4" t="n">
+      <c r="N301" s="8" t="n">
         <v>79.774</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
@@ -23594,7 +23609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G302" s="4" t="n">
+      <c r="G302" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -23627,7 +23642,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N302" s="4" t="n">
+      <c r="N302" s="8" t="n">
         <v>80.255</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
@@ -23673,7 +23688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G303" s="4" t="n">
+      <c r="G303" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
@@ -23706,7 +23721,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N303" s="4" t="n">
+      <c r="N303" s="8" t="n">
         <v>80.316</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
@@ -23752,7 +23767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G304" s="4" t="n">
+      <c r="G304" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -23785,7 +23800,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N304" s="4" t="n">
+      <c r="N304" s="8" t="n">
         <v>80.395</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
@@ -23831,7 +23846,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G305" s="4" t="n">
+      <c r="G305" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -23864,7 +23879,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N305" s="4" t="n">
+      <c r="N305" s="8" t="n">
         <v>80.408</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
@@ -23910,7 +23925,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G306" s="4" t="n">
+      <c r="G306" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -23943,7 +23958,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N306" s="4" t="n">
+      <c r="N306" s="8" t="n">
         <v>80.67400000000001</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
@@ -23989,7 +24004,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G307" s="4" t="n">
+      <c r="G307" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -24022,7 +24037,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n">
+      <c r="N307" s="8" t="n">
         <v>80.18899999999999</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
@@ -24068,7 +24083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G308" s="4" t="n">
+      <c r="G308" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -24101,7 +24116,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N308" s="4" t="n">
+      <c r="N308" s="8" t="n">
         <v>80.69199999999999</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
@@ -24147,7 +24162,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G309" s="4" t="n">
+      <c r="G309" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
@@ -24180,7 +24195,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N309" s="4" t="n">
+      <c r="N309" s="8" t="n">
         <v>80.23399999999999</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
@@ -24226,7 +24241,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G310" s="4" t="n">
+      <c r="G310" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
@@ -24259,7 +24274,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N310" s="4" t="n">
+      <c r="N310" s="8" t="n">
         <v>79.989</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
@@ -24305,7 +24320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G311" s="4" t="n">
+      <c r="G311" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
@@ -24338,7 +24353,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n">
+      <c r="N311" s="8" t="n">
         <v>80.45999999999999</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
@@ -24384,7 +24399,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G312" s="4" t="n">
+      <c r="G312" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
@@ -24417,7 +24432,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N312" s="4" t="n">
+      <c r="N312" s="8" t="n">
         <v>80.068</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
@@ -24463,7 +24478,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n">
+      <c r="G313" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
@@ -24496,7 +24511,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="8" t="n">
         <v>79.241</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
@@ -24542,7 +24557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G314" s="4" t="n">
+      <c r="G314" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
@@ -24575,7 +24590,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N314" s="4" t="n">
+      <c r="N314" s="8" t="n">
         <v>79.026</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
@@ -24621,7 +24636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G315" s="4" t="n">
+      <c r="G315" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
@@ -24654,7 +24669,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N315" s="4" t="n">
+      <c r="N315" s="8" t="n">
         <v>80.274</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
@@ -24700,7 +24715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G316" s="4" t="n">
+      <c r="G316" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
@@ -24733,7 +24748,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N316" s="4" t="n">
+      <c r="N316" s="8" t="n">
         <v>79.499</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
@@ -24779,7 +24794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G317" s="4" t="n">
+      <c r="G317" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
@@ -24812,7 +24827,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N317" s="4" t="n">
+      <c r="N317" s="8" t="n">
         <v>80.117</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
@@ -24858,7 +24873,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G318" s="4" t="n">
+      <c r="G318" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
@@ -24891,7 +24906,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N318" s="4" t="n">
+      <c r="N318" s="8" t="n">
         <v>79.53100000000001</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
@@ -24937,7 +24952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G319" s="4" t="n">
+      <c r="G319" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
@@ -24970,7 +24985,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N319" s="4" t="n">
+      <c r="N319" s="8" t="n">
         <v>79.29000000000001</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
@@ -25016,7 +25031,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G320" s="4" t="n">
+      <c r="G320" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
@@ -25049,7 +25064,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N320" s="4" t="n">
+      <c r="N320" s="8" t="n">
         <v>78.518</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
@@ -25095,7 +25110,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G321" s="4" t="n">
+      <c r="G321" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
@@ -25128,7 +25143,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N321" s="4" t="n">
+      <c r="N321" s="8" t="n">
         <v>78.56699999999999</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
@@ -25174,7 +25189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G322" s="4" t="n">
+      <c r="G322" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
@@ -25207,7 +25222,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N322" s="4" t="n">
+      <c r="N322" s="8" t="n">
         <v>78.07599999999999</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
@@ -25253,7 +25268,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G323" s="4" t="n">
+      <c r="G323" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
@@ -25286,7 +25301,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N323" s="4" t="n">
+      <c r="N323" s="8" t="n">
         <v>77.208</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
@@ -25332,7 +25347,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G324" s="4" t="n">
+      <c r="G324" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
@@ -25365,7 +25380,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N324" s="4" t="n">
+      <c r="N324" s="8" t="n">
         <v>76.672</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
@@ -25411,7 +25426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G325" s="4" t="n">
+      <c r="G325" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -25444,7 +25459,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N325" s="4" t="n">
+      <c r="N325" s="8" t="n">
         <v>76.128</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
@@ -25490,7 +25505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G326" s="4" t="n">
+      <c r="G326" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
@@ -25523,7 +25538,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n">
+      <c r="N326" s="8" t="n">
         <v>75.57899999999999</v>
       </c>
       <c r="O326" s="4" t="inlineStr">
@@ -25569,7 +25584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G327" s="4" t="n">
+      <c r="G327" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
@@ -25602,7 +25617,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N327" s="4" t="n">
+      <c r="N327" s="8" t="n">
         <v>75.026</v>
       </c>
       <c r="O327" s="4" t="inlineStr">
@@ -25648,7 +25663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G328" s="4" t="n">
+      <c r="G328" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -25681,7 +25696,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N328" s="4" t="n">
+      <c r="N328" s="8" t="n">
         <v>74.18899999999999</v>
       </c>
       <c r="O328" s="4" t="inlineStr">
@@ -25727,7 +25742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G329" s="4" t="n">
+      <c r="G329" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -25760,7 +25775,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n">
+      <c r="N329" s="8" t="n">
         <v>72.125</v>
       </c>
       <c r="O329" s="4" t="inlineStr">
@@ -25806,7 +25821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G330" s="4" t="n">
+      <c r="G330" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
@@ -25839,7 +25854,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N330" s="4" t="n">
+      <c r="N330" s="8" t="n">
         <v>68.58</v>
       </c>
       <c r="O330" s="4" t="inlineStr">
@@ -25885,7 +25900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G331" s="4" t="n">
+      <c r="G331" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
@@ -25918,7 +25933,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n">
+      <c r="N331" s="8" t="n">
         <v>60.016</v>
       </c>
       <c r="O331" s="4" t="inlineStr">
@@ -25964,7 +25979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G332" s="4" t="n">
+      <c r="G332" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
@@ -25997,7 +26012,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N332" s="4" t="n">
+      <c r="N332" s="8" t="n">
         <v>60.412</v>
       </c>
       <c r="O332" s="4" t="inlineStr">
@@ -26043,7 +26058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G333" s="4" t="n">
+      <c r="G333" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
@@ -26076,7 +26091,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N333" s="4" t="n">
+      <c r="N333" s="8" t="n">
         <v>67.23</v>
       </c>
       <c r="O333" s="4" t="inlineStr">
@@ -26122,7 +26137,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n">
+      <c r="G334" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
@@ -26155,7 +26170,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N334" s="4" t="n">
+      <c r="N334" s="8" t="n">
         <v>67.349</v>
       </c>
       <c r="O334" s="4" t="inlineStr">
@@ -26201,7 +26216,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n">
+      <c r="G335" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
@@ -26234,7 +26249,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N335" s="4" t="n">
+      <c r="N335" s="8" t="n">
         <v>67.524</v>
       </c>
       <c r="O335" s="4" t="inlineStr">
@@ -26280,7 +26295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G336" s="4" t="n">
+      <c r="G336" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
@@ -26313,7 +26328,7 @@
           <t>Tasa de participación laboral masculina</t>
         </is>
       </c>
-      <c r="N336" s="4" t="n">
+      <c r="N336" s="8" t="n">
         <v>67.523</v>
       </c>
       <c r="O336" s="4" t="inlineStr">
@@ -26359,7 +26374,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G337" s="4" t="n">
+      <c r="G337" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
@@ -26440,7 +26455,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n">
+      <c r="G338" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H338" s="4" t="inlineStr">
@@ -26521,7 +26536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n">
+      <c r="G339" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H339" s="4" t="inlineStr">
@@ -26602,7 +26617,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n">
+      <c r="G340" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H340" s="4" t="inlineStr">
@@ -26683,7 +26698,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G341" s="4" t="n">
+      <c r="G341" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H341" s="4" t="inlineStr">
@@ -26764,7 +26779,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G342" s="4" t="n">
+      <c r="G342" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
@@ -26845,7 +26860,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G343" s="4" t="n">
+      <c r="G343" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
@@ -26926,7 +26941,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G344" s="4" t="n">
+      <c r="G344" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H344" s="4" t="inlineStr">
@@ -27007,7 +27022,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n">
+      <c r="G345" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
@@ -27088,7 +27103,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n">
+      <c r="G346" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
@@ -27169,7 +27184,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n">
+      <c r="G347" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H347" s="4" t="inlineStr">
@@ -27250,7 +27265,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n">
+      <c r="G348" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
@@ -27331,7 +27346,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G349" s="4" t="n">
+      <c r="G349" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
@@ -27412,7 +27427,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G350" s="4" t="n">
+      <c r="G350" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
@@ -27493,7 +27508,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G351" s="4" t="n">
+      <c r="G351" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
@@ -27574,7 +27589,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G352" s="4" t="n">
+      <c r="G352" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
@@ -27655,7 +27670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G353" s="4" t="n">
+      <c r="G353" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
@@ -27736,7 +27751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G354" s="4" t="n">
+      <c r="G354" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
@@ -27817,7 +27832,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G355" s="4" t="n">
+      <c r="G355" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
@@ -27898,7 +27913,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G356" s="4" t="n">
+      <c r="G356" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
@@ -27979,7 +27994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G357" s="4" t="n">
+      <c r="G357" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -28060,7 +28075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G358" s="4" t="n">
+      <c r="G358" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H358" s="4" t="inlineStr">
@@ -28141,7 +28156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G359" s="4" t="n">
+      <c r="G359" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
@@ -28222,7 +28237,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n">
+      <c r="G360" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
@@ -28303,7 +28318,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G361" s="4" t="n">
+      <c r="G361" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H361" s="4" t="inlineStr">
@@ -28384,7 +28399,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G362" s="4" t="n">
+      <c r="G362" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H362" s="4" t="inlineStr">
@@ -28465,7 +28480,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G363" s="4" t="n">
+      <c r="G363" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H363" s="4" t="inlineStr">
@@ -28546,7 +28561,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G364" s="4" t="n">
+      <c r="G364" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H364" s="4" t="inlineStr">
@@ -28627,7 +28642,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G365" s="4" t="n">
+      <c r="G365" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H365" s="4" t="inlineStr">
@@ -28708,7 +28723,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G366" s="4" t="n">
+      <c r="G366" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H366" s="4" t="inlineStr">
@@ -28789,7 +28804,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G367" s="4" t="n">
+      <c r="G367" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H367" s="4" t="inlineStr">
@@ -28870,7 +28885,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G368" s="4" t="n">
+      <c r="G368" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H368" s="4" t="inlineStr">
@@ -28951,7 +28966,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G369" s="4" t="n">
+      <c r="G369" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H369" s="4" t="inlineStr">
@@ -29032,7 +29047,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G370" s="4" t="n">
+      <c r="G370" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H370" s="4" t="inlineStr">
@@ -29113,7 +29128,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G371" s="4" t="n">
+      <c r="G371" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H371" s="4" t="inlineStr">
@@ -29194,7 +29209,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G372" s="4" t="n">
+      <c r="G372" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H372" s="4" t="inlineStr">
@@ -29275,7 +29290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G373" s="4" t="n">
+      <c r="G373" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H373" s="4" t="inlineStr">
@@ -29356,7 +29371,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G374" s="4" t="n">
+      <c r="G374" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H374" s="4" t="inlineStr">
@@ -29437,7 +29452,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G375" s="4" t="n">
+      <c r="G375" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H375" s="4" t="inlineStr">
@@ -29518,7 +29533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G376" s="4" t="n">
+      <c r="G376" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H376" s="4" t="inlineStr">
@@ -29599,7 +29614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G377" s="4" t="n">
+      <c r="G377" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H377" s="4" t="inlineStr">
@@ -29680,7 +29695,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G378" s="4" t="n">
+      <c r="G378" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H378" s="4" t="inlineStr">
@@ -29761,7 +29776,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G379" s="4" t="n">
+      <c r="G379" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H379" s="4" t="inlineStr">
@@ -29842,7 +29857,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G380" s="4" t="n">
+      <c r="G380" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H380" s="4" t="inlineStr">
@@ -29923,7 +29938,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G381" s="4" t="n">
+      <c r="G381" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H381" s="4" t="inlineStr">
@@ -30004,7 +30019,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G382" s="4" t="n">
+      <c r="G382" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H382" s="4" t="inlineStr">
@@ -30085,7 +30100,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G383" s="4" t="n">
+      <c r="G383" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H383" s="4" t="inlineStr">
@@ -30166,7 +30181,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G384" s="4" t="n">
+      <c r="G384" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H384" s="4" t="inlineStr">
@@ -30247,7 +30262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G385" s="4" t="n">
+      <c r="G385" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H385" s="4" t="inlineStr">
@@ -30328,7 +30343,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G386" s="4" t="n">
+      <c r="G386" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H386" s="4" t="inlineStr">
@@ -30409,7 +30424,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G387" s="4" t="n">
+      <c r="G387" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H387" s="4" t="inlineStr">
@@ -30490,7 +30505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G388" s="4" t="n">
+      <c r="G388" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H388" s="4" t="inlineStr">
@@ -30571,7 +30586,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G389" s="4" t="n">
+      <c r="G389" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H389" s="4" t="inlineStr">
@@ -30652,7 +30667,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G390" s="4" t="n">
+      <c r="G390" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H390" s="4" t="inlineStr">
@@ -30733,7 +30748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G391" s="4" t="n">
+      <c r="G391" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H391" s="4" t="inlineStr">
@@ -30814,7 +30829,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G392" s="4" t="n">
+      <c r="G392" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H392" s="4" t="inlineStr">
@@ -30895,7 +30910,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G393" s="4" t="n">
+      <c r="G393" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H393" s="4" t="inlineStr">
@@ -30976,7 +30991,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G394" s="4" t="n">
+      <c r="G394" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H394" s="4" t="inlineStr">
@@ -31057,7 +31072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G395" s="4" t="n">
+      <c r="G395" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H395" s="4" t="inlineStr">
@@ -31138,7 +31153,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G396" s="4" t="n">
+      <c r="G396" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H396" s="4" t="inlineStr">
@@ -31219,7 +31234,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G397" s="4" t="n">
+      <c r="G397" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H397" s="4" t="inlineStr">
@@ -31300,7 +31315,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n">
+      <c r="G398" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H398" s="4" t="inlineStr">
@@ -31381,7 +31396,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G399" s="4" t="n">
+      <c r="G399" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H399" s="4" t="inlineStr">
@@ -31462,7 +31477,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G400" s="4" t="n">
+      <c r="G400" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H400" s="4" t="inlineStr">
@@ -31543,7 +31558,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G401" s="4" t="n">
+      <c r="G401" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H401" s="4" t="inlineStr">
@@ -31624,7 +31639,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G402" s="4" t="n">
+      <c r="G402" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H402" s="4" t="inlineStr">
@@ -31705,7 +31720,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G403" s="4" t="n">
+      <c r="G403" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H403" s="4" t="inlineStr">
@@ -31786,7 +31801,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G404" s="4" t="n">
+      <c r="G404" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H404" s="4" t="inlineStr">
@@ -31867,7 +31882,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n">
+      <c r="G405" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H405" s="4" t="inlineStr">
@@ -31948,7 +31963,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G406" s="4" t="n">
+      <c r="G406" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H406" s="4" t="inlineStr">
@@ -32029,7 +32044,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G407" s="4" t="n">
+      <c r="G407" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H407" s="4" t="inlineStr">
@@ -32110,7 +32125,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G408" s="4" t="n">
+      <c r="G408" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H408" s="4" t="inlineStr">
@@ -32191,7 +32206,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G409" s="4" t="n">
+      <c r="G409" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H409" s="4" t="inlineStr">
@@ -32272,7 +32287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G410" s="4" t="n">
+      <c r="G410" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H410" s="4" t="inlineStr">
@@ -32353,7 +32368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G411" s="4" t="n">
+      <c r="G411" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -32434,7 +32449,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G412" s="4" t="n">
+      <c r="G412" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H412" s="4" t="inlineStr">
@@ -32515,7 +32530,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G413" s="4" t="n">
+      <c r="G413" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H413" s="4" t="inlineStr">
@@ -32596,7 +32611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G414" s="4" t="n">
+      <c r="G414" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H414" s="4" t="inlineStr">
@@ -32677,7 +32692,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G415" s="4" t="n">
+      <c r="G415" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H415" s="4" t="inlineStr">
@@ -32758,7 +32773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G416" s="4" t="n">
+      <c r="G416" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H416" s="4" t="inlineStr">
@@ -32839,7 +32854,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G417" s="4" t="n">
+      <c r="G417" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H417" s="4" t="inlineStr">
@@ -32920,7 +32935,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G418" s="4" t="n">
+      <c r="G418" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H418" s="4" t="inlineStr">
@@ -33001,7 +33016,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G419" s="4" t="n">
+      <c r="G419" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H419" s="4" t="inlineStr">
@@ -33082,7 +33097,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G420" s="4" t="n">
+      <c r="G420" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H420" s="4" t="inlineStr">
@@ -33163,7 +33178,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G421" s="4" t="n">
+      <c r="G421" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H421" s="4" t="inlineStr">
@@ -33244,7 +33259,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G422" s="4" t="n">
+      <c r="G422" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H422" s="4" t="inlineStr">
@@ -33325,7 +33340,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n">
+      <c r="G423" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H423" s="4" t="inlineStr">
@@ -33406,7 +33421,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n">
+      <c r="G424" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H424" s="4" t="inlineStr">
@@ -33487,7 +33502,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n">
+      <c r="G425" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H425" s="4" t="inlineStr">
@@ -33568,7 +33583,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n">
+      <c r="G426" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H426" s="4" t="inlineStr">
@@ -33649,7 +33664,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G427" s="4" t="n">
+      <c r="G427" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H427" s="4" t="inlineStr">
@@ -33730,7 +33745,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G428" s="4" t="n">
+      <c r="G428" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H428" s="4" t="inlineStr">
@@ -33811,7 +33826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G429" s="4" t="n">
+      <c r="G429" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H429" s="4" t="inlineStr">
@@ -33892,7 +33907,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G430" s="4" t="n">
+      <c r="G430" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H430" s="4" t="inlineStr">
@@ -33973,7 +33988,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G431" s="4" t="n">
+      <c r="G431" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H431" s="4" t="inlineStr">
@@ -34054,7 +34069,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G432" s="4" t="n">
+      <c r="G432" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -34135,7 +34150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G433" s="4" t="n">
+      <c r="G433" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H433" s="4" t="inlineStr">
@@ -34216,7 +34231,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G434" s="4" t="n">
+      <c r="G434" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H434" s="4" t="inlineStr">
@@ -34297,7 +34312,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G435" s="4" t="n">
+      <c r="G435" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H435" s="4" t="inlineStr">
@@ -34378,7 +34393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G436" s="4" t="n">
+      <c r="G436" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H436" s="4" t="inlineStr">
@@ -34459,7 +34474,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G437" s="4" t="n">
+      <c r="G437" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H437" s="4" t="inlineStr">
@@ -34540,7 +34555,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G438" s="4" t="n">
+      <c r="G438" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H438" s="4" t="inlineStr">
@@ -34621,7 +34636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G439" s="4" t="n">
+      <c r="G439" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H439" s="4" t="inlineStr">
@@ -34702,7 +34717,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G440" s="4" t="n">
+      <c r="G440" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H440" s="4" t="inlineStr">
@@ -34783,7 +34798,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G441" s="4" t="n">
+      <c r="G441" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H441" s="4" t="inlineStr">
@@ -34864,7 +34879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G442" s="4" t="n">
+      <c r="G442" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H442" s="4" t="inlineStr">
@@ -34945,7 +34960,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G443" s="4" t="n">
+      <c r="G443" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H443" s="4" t="inlineStr">
@@ -35026,7 +35041,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G444" s="4" t="n">
+      <c r="G444" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H444" s="4" t="inlineStr">
@@ -35107,7 +35122,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G445" s="4" t="n">
+      <c r="G445" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H445" s="4" t="inlineStr">
@@ -35188,7 +35203,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G446" s="4" t="n">
+      <c r="G446" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H446" s="4" t="inlineStr">
@@ -35269,7 +35284,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G447" s="4" t="n">
+      <c r="G447" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H447" s="4" t="inlineStr">
@@ -35350,7 +35365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G448" s="4" t="n">
+      <c r="G448" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H448" s="4" t="inlineStr">
@@ -35431,7 +35446,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G449" s="4" t="n">
+      <c r="G449" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H449" s="4" t="inlineStr">
@@ -35512,7 +35527,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n">
+      <c r="G450" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H450" s="4" t="inlineStr">
@@ -35593,7 +35608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n">
+      <c r="G451" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H451" s="4" t="inlineStr">
@@ -35674,7 +35689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G452" s="4" t="n">
+      <c r="G452" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H452" s="4" t="inlineStr">
@@ -35755,7 +35770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G453" s="4" t="n">
+      <c r="G453" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H453" s="4" t="inlineStr">
@@ -35836,7 +35851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G454" s="4" t="n">
+      <c r="G454" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H454" s="4" t="inlineStr">
@@ -35917,7 +35932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G455" s="4" t="n">
+      <c r="G455" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H455" s="4" t="inlineStr">
@@ -35998,7 +36013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G456" s="4" t="n">
+      <c r="G456" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H456" s="4" t="inlineStr">
@@ -36079,7 +36094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G457" s="4" t="n">
+      <c r="G457" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H457" s="4" t="inlineStr">
@@ -36160,7 +36175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G458" s="4" t="n">
+      <c r="G458" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H458" s="4" t="inlineStr">
@@ -36241,7 +36256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n">
+      <c r="G459" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H459" s="4" t="inlineStr">
@@ -36322,7 +36337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n">
+      <c r="G460" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H460" s="4" t="inlineStr">
@@ -36403,7 +36418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n">
+      <c r="G461" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H461" s="4" t="inlineStr">
@@ -36484,7 +36499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G462" s="4" t="n">
+      <c r="G462" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H462" s="4" t="inlineStr">
@@ -36565,7 +36580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G463" s="4" t="n">
+      <c r="G463" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H463" s="4" t="inlineStr">
@@ -36646,7 +36661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G464" s="4" t="n">
+      <c r="G464" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H464" s="4" t="inlineStr">
@@ -36727,7 +36742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G465" s="4" t="n">
+      <c r="G465" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H465" s="4" t="inlineStr">
@@ -36808,7 +36823,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G466" s="4" t="n">
+      <c r="G466" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H466" s="4" t="inlineStr">
@@ -36889,7 +36904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G467" s="4" t="n">
+      <c r="G467" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H467" s="4" t="inlineStr">
@@ -36970,7 +36985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G468" s="4" t="n">
+      <c r="G468" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H468" s="4" t="inlineStr">
@@ -37051,7 +37066,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G469" s="4" t="n">
+      <c r="G469" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
@@ -37132,7 +37147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G470" s="4" t="n">
+      <c r="G470" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
@@ -37213,7 +37228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G471" s="4" t="n">
+      <c r="G471" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
@@ -37290,7 +37305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G472" s="4" t="n">
+      <c r="G472" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
@@ -37367,7 +37382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G473" s="4" t="n">
+      <c r="G473" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
@@ -37444,7 +37459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G474" s="4" t="n">
+      <c r="G474" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H474" s="4" t="inlineStr">
@@ -37521,7 +37536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G475" s="4" t="n">
+      <c r="G475" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H475" s="4" t="inlineStr">
@@ -37598,7 +37613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G476" s="4" t="n">
+      <c r="G476" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H476" s="4" t="inlineStr">
@@ -37675,7 +37690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G477" s="4" t="n">
+      <c r="G477" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H477" s="4" t="inlineStr">
@@ -37752,7 +37767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G478" s="4" t="n">
+      <c r="G478" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H478" s="4" t="inlineStr">
@@ -37829,7 +37844,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G479" s="4" t="n">
+      <c r="G479" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H479" s="4" t="inlineStr">
@@ -37906,7 +37921,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G480" s="4" t="n">
+      <c r="G480" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H480" s="4" t="inlineStr">
@@ -37983,7 +37998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G481" s="4" t="n">
+      <c r="G481" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H481" s="4" t="inlineStr">
@@ -38060,7 +38075,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G482" s="4" t="n">
+      <c r="G482" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H482" s="4" t="inlineStr">
@@ -38137,7 +38152,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G483" s="4" t="n">
+      <c r="G483" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H483" s="4" t="inlineStr">
@@ -38214,7 +38229,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G484" s="4" t="n">
+      <c r="G484" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H484" s="4" t="inlineStr">
@@ -38291,7 +38306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G485" s="4" t="n">
+      <c r="G485" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H485" s="4" t="inlineStr">
@@ -38368,7 +38383,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G486" s="4" t="n">
+      <c r="G486" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H486" s="4" t="inlineStr">
@@ -38445,7 +38460,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G487" s="4" t="n">
+      <c r="G487" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H487" s="4" t="inlineStr">
@@ -38522,7 +38537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G488" s="4" t="n">
+      <c r="G488" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H488" s="4" t="inlineStr">
@@ -38599,7 +38614,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G489" s="4" t="n">
+      <c r="G489" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H489" s="4" t="inlineStr">
@@ -38676,7 +38691,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G490" s="4" t="n">
+      <c r="G490" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H490" s="4" t="inlineStr">
@@ -38753,7 +38768,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G491" s="4" t="n">
+      <c r="G491" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H491" s="4" t="inlineStr">
@@ -38830,7 +38845,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G492" s="4" t="n">
+      <c r="G492" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H492" s="4" t="inlineStr">
@@ -38907,7 +38922,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G493" s="4" t="n">
+      <c r="G493" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H493" s="4" t="inlineStr">
@@ -38984,7 +38999,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G494" s="4" t="n">
+      <c r="G494" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H494" s="4" t="inlineStr">
@@ -39061,7 +39076,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G495" s="4" t="n">
+      <c r="G495" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H495" s="4" t="inlineStr">
@@ -39138,7 +39153,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G496" s="4" t="n">
+      <c r="G496" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H496" s="4" t="inlineStr">
@@ -39215,7 +39230,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G497" s="4" t="n">
+      <c r="G497" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H497" s="4" t="inlineStr">
@@ -39292,7 +39307,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G498" s="4" t="n">
+      <c r="G498" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H498" s="4" t="inlineStr">
@@ -39369,7 +39384,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G499" s="4" t="n">
+      <c r="G499" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H499" s="4" t="inlineStr">
@@ -39446,7 +39461,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G500" s="4" t="n">
+      <c r="G500" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H500" s="4" t="inlineStr">
@@ -39523,7 +39538,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G501" s="4" t="n">
+      <c r="G501" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H501" s="4" t="inlineStr">
@@ -39600,7 +39615,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G502" s="4" t="n">
+      <c r="G502" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H502" s="4" t="inlineStr">
@@ -39633,7 +39648,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N502" s="4" t="n">
+      <c r="N502" s="8" t="n">
         <v>15.588</v>
       </c>
       <c r="O502" s="4" t="inlineStr">
@@ -39679,7 +39694,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G503" s="4" t="n">
+      <c r="G503" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H503" s="4" t="inlineStr">
@@ -39712,7 +39727,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N503" s="4" t="n">
+      <c r="N503" s="8" t="n">
         <v>12.884</v>
       </c>
       <c r="O503" s="4" t="inlineStr">
@@ -39758,7 +39773,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G504" s="4" t="n">
+      <c r="G504" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H504" s="4" t="inlineStr">
@@ -39791,7 +39806,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N504" s="4" t="n">
+      <c r="N504" s="8" t="n">
         <v>11.019</v>
       </c>
       <c r="O504" s="4" t="inlineStr">
@@ -39837,7 +39852,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G505" s="4" t="n">
+      <c r="G505" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H505" s="4" t="inlineStr">
@@ -39870,7 +39885,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N505" s="4" t="n">
+      <c r="N505" s="8" t="n">
         <v>14.216</v>
       </c>
       <c r="O505" s="4" t="inlineStr">
@@ -39916,7 +39931,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G506" s="4" t="n">
+      <c r="G506" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H506" s="4" t="inlineStr">
@@ -39949,7 +39964,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N506" s="4" t="n">
+      <c r="N506" s="8" t="n">
         <v>17.041</v>
       </c>
       <c r="O506" s="4" t="inlineStr">
@@ -39995,7 +40010,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G507" s="4" t="n">
+      <c r="G507" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H507" s="4" t="inlineStr">
@@ -40028,7 +40043,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N507" s="4" t="n">
+      <c r="N507" s="8" t="n">
         <v>19.617</v>
       </c>
       <c r="O507" s="4" t="inlineStr">
@@ -40074,7 +40089,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G508" s="4" t="n">
+      <c r="G508" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H508" s="4" t="inlineStr">
@@ -40107,7 +40122,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N508" s="4" t="n">
+      <c r="N508" s="8" t="n">
         <v>18.807</v>
       </c>
       <c r="O508" s="4" t="inlineStr">
@@ -40153,7 +40168,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G509" s="4" t="n">
+      <c r="G509" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H509" s="4" t="inlineStr">
@@ -40186,7 +40201,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N509" s="4" t="n">
+      <c r="N509" s="8" t="n">
         <v>18.757</v>
       </c>
       <c r="O509" s="4" t="inlineStr">
@@ -40232,7 +40247,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G510" s="4" t="n">
+      <c r="G510" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H510" s="4" t="inlineStr">
@@ -40265,7 +40280,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N510" s="4" t="n">
+      <c r="N510" s="8" t="n">
         <v>24.329</v>
       </c>
       <c r="O510" s="4" t="inlineStr">
@@ -40311,7 +40326,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G511" s="4" t="n">
+      <c r="G511" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H511" s="4" t="inlineStr">
@@ -40344,7 +40359,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N511" s="4" t="n">
+      <c r="N511" s="8" t="n">
         <v>23.396</v>
       </c>
       <c r="O511" s="4" t="inlineStr">
@@ -40390,7 +40405,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G512" s="4" t="n">
+      <c r="G512" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H512" s="4" t="inlineStr">
@@ -40423,7 +40438,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N512" s="4" t="n">
+      <c r="N512" s="8" t="n">
         <v>21.94</v>
       </c>
       <c r="O512" s="4" t="inlineStr">
@@ -40469,7 +40484,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G513" s="4" t="n">
+      <c r="G513" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H513" s="4" t="inlineStr">
@@ -40502,7 +40517,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N513" s="4" t="n">
+      <c r="N513" s="8" t="n">
         <v>27.187</v>
       </c>
       <c r="O513" s="4" t="inlineStr">
@@ -40548,7 +40563,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G514" s="4" t="n">
+      <c r="G514" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H514" s="4" t="inlineStr">
@@ -40581,7 +40596,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N514" s="4" t="n">
+      <c r="N514" s="8" t="n">
         <v>27.914</v>
       </c>
       <c r="O514" s="4" t="inlineStr">
@@ -40627,7 +40642,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G515" s="4" t="n">
+      <c r="G515" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H515" s="4" t="inlineStr">
@@ -40660,7 +40675,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N515" s="4" t="n">
+      <c r="N515" s="8" t="n">
         <v>25.273</v>
       </c>
       <c r="O515" s="4" t="inlineStr">
@@ -40706,7 +40721,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G516" s="4" t="n">
+      <c r="G516" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H516" s="4" t="inlineStr">
@@ -40739,7 +40754,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N516" s="4" t="n">
+      <c r="N516" s="8" t="n">
         <v>18.247</v>
       </c>
       <c r="O516" s="4" t="inlineStr">
@@ -40785,7 +40800,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G517" s="4" t="n">
+      <c r="G517" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H517" s="4" t="inlineStr">
@@ -40818,7 +40833,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N517" s="4" t="n">
+      <c r="N517" s="8" t="n">
         <v>15.361</v>
       </c>
       <c r="O517" s="4" t="inlineStr">
@@ -40864,7 +40879,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G518" s="4" t="n">
+      <c r="G518" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H518" s="4" t="inlineStr">
@@ -40897,7 +40912,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N518" s="4" t="n">
+      <c r="N518" s="8" t="n">
         <v>13.574</v>
       </c>
       <c r="O518" s="4" t="inlineStr">
@@ -40943,7 +40958,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G519" s="4" t="n">
+      <c r="G519" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H519" s="4" t="inlineStr">
@@ -40976,7 +40991,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N519" s="4" t="n">
+      <c r="N519" s="8" t="n">
         <v>12.354</v>
       </c>
       <c r="O519" s="4" t="inlineStr">
@@ -41022,7 +41037,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G520" s="4" t="n">
+      <c r="G520" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H520" s="4" t="inlineStr">
@@ -41055,7 +41070,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N520" s="4" t="n">
+      <c r="N520" s="8" t="n">
         <v>12.126</v>
       </c>
       <c r="O520" s="4" t="inlineStr">
@@ -41101,7 +41116,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G521" s="4" t="n">
+      <c r="G521" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H521" s="4" t="inlineStr">
@@ -41134,7 +41149,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N521" s="4" t="n">
+      <c r="N521" s="8" t="n">
         <v>14.178</v>
       </c>
       <c r="O521" s="4" t="inlineStr">
@@ -41180,7 +41195,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G522" s="4" t="n">
+      <c r="G522" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H522" s="4" t="inlineStr">
@@ -41213,7 +41228,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N522" s="4" t="n">
+      <c r="N522" s="8" t="n">
         <v>14.048</v>
       </c>
       <c r="O522" s="4" t="inlineStr">
@@ -41259,7 +41274,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G523" s="4" t="n">
+      <c r="G523" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H523" s="4" t="inlineStr">
@@ -41292,7 +41307,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N523" s="4" t="n">
+      <c r="N523" s="8" t="n">
         <v>14.089</v>
       </c>
       <c r="O523" s="4" t="inlineStr">
@@ -41338,7 +41353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G524" s="4" t="n">
+      <c r="G524" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H524" s="4" t="inlineStr">
@@ -41371,7 +41386,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N524" s="4" t="n">
+      <c r="N524" s="8" t="n">
         <v>16.224</v>
       </c>
       <c r="O524" s="4" t="inlineStr">
@@ -41417,7 +41432,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G525" s="4" t="n">
+      <c r="G525" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H525" s="4" t="inlineStr">
@@ -41450,7 +41465,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N525" s="4" t="n">
+      <c r="N525" s="8" t="n">
         <v>14.767</v>
       </c>
       <c r="O525" s="4" t="inlineStr">
@@ -41496,7 +41511,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G526" s="4" t="n">
+      <c r="G526" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H526" s="4" t="inlineStr">
@@ -41529,7 +41544,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N526" s="4" t="n">
+      <c r="N526" s="8" t="n">
         <v>13.334</v>
       </c>
       <c r="O526" s="4" t="inlineStr">
@@ -41575,7 +41590,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G527" s="4" t="n">
+      <c r="G527" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H527" s="4" t="inlineStr">
@@ -41608,7 +41623,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N527" s="4" t="n">
+      <c r="N527" s="8" t="n">
         <v>11.677</v>
       </c>
       <c r="O527" s="4" t="inlineStr">
@@ -41654,7 +41669,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G528" s="4" t="n">
+      <c r="G528" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H528" s="4" t="inlineStr">
@@ -41687,7 +41702,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N528" s="4" t="n">
+      <c r="N528" s="8" t="n">
         <v>12.247</v>
       </c>
       <c r="O528" s="4" t="inlineStr">
@@ -41733,7 +41748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G529" s="4" t="n">
+      <c r="G529" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H529" s="4" t="inlineStr">
@@ -41766,7 +41781,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N529" s="4" t="n">
+      <c r="N529" s="8" t="n">
         <v>12.034</v>
       </c>
       <c r="O529" s="4" t="inlineStr">
@@ -41812,7 +41827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G530" s="4" t="n">
+      <c r="G530" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H530" s="4" t="inlineStr">
@@ -41845,7 +41860,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N530" s="4" t="n">
+      <c r="N530" s="8" t="n">
         <v>11.767</v>
       </c>
       <c r="O530" s="4" t="inlineStr">
@@ -41891,7 +41906,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G531" s="4" t="n">
+      <c r="G531" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H531" s="4" t="inlineStr">
@@ -41924,7 +41939,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N531" s="4" t="n">
+      <c r="N531" s="8" t="n">
         <v>13.608</v>
       </c>
       <c r="O531" s="4" t="inlineStr">
@@ -41970,7 +41985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G532" s="4" t="n">
+      <c r="G532" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H532" s="4" t="inlineStr">
@@ -42003,7 +42018,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N532" s="4" t="n">
+      <c r="N532" s="8" t="n">
         <v>12.943</v>
       </c>
       <c r="O532" s="4" t="inlineStr">
@@ -42049,7 +42064,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G533" s="4" t="n">
+      <c r="G533" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H533" s="4" t="inlineStr">
@@ -42082,7 +42097,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N533" s="4" t="n">
+      <c r="N533" s="8" t="n">
         <v>10.58</v>
       </c>
       <c r="O533" s="4" t="inlineStr">
@@ -42128,7 +42143,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G534" s="4" t="n">
+      <c r="G534" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H534" s="4" t="inlineStr">
@@ -42161,7 +42176,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N534" s="4" t="n">
+      <c r="N534" s="8" t="n">
         <v>10.274</v>
       </c>
       <c r="O534" s="4" t="inlineStr">
@@ -42207,7 +42222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G535" s="4" t="n">
+      <c r="G535" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H535" s="4" t="inlineStr">
@@ -42240,7 +42255,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N535" s="4" t="n">
+      <c r="N535" s="8" t="n">
         <v>10.158</v>
       </c>
       <c r="O535" s="4" t="inlineStr">
@@ -42286,7 +42301,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G536" s="4" t="n">
+      <c r="G536" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H536" s="4" t="inlineStr">
@@ -42319,7 +42334,7 @@
           <t>Tasa de desempleo juvenil</t>
         </is>
       </c>
-      <c r="N536" s="4" t="n">
+      <c r="N536" s="8" t="n">
         <v>10.444</v>
       </c>
       <c r="O536" s="4" t="inlineStr">
@@ -42365,7 +42380,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G537" s="4" t="n">
+      <c r="G537" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H537" s="4" t="inlineStr">
@@ -42442,7 +42457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G538" s="4" t="n">
+      <c r="G538" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H538" s="4" t="inlineStr">
@@ -42519,7 +42534,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G539" s="4" t="n">
+      <c r="G539" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H539" s="4" t="inlineStr">
@@ -42596,7 +42611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G540" s="4" t="n">
+      <c r="G540" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H540" s="4" t="inlineStr">
@@ -42673,7 +42688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G541" s="4" t="n">
+      <c r="G541" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H541" s="4" t="inlineStr">
@@ -42750,7 +42765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G542" s="4" t="n">
+      <c r="G542" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H542" s="4" t="inlineStr">
@@ -42827,7 +42842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G543" s="4" t="n">
+      <c r="G543" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H543" s="4" t="inlineStr">
@@ -42904,7 +42919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G544" s="4" t="n">
+      <c r="G544" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H544" s="4" t="inlineStr">
@@ -42981,7 +42996,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G545" s="4" t="n">
+      <c r="G545" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H545" s="4" t="inlineStr">
@@ -43058,7 +43073,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G546" s="4" t="n">
+      <c r="G546" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H546" s="4" t="inlineStr">
@@ -43135,7 +43150,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G547" s="4" t="n">
+      <c r="G547" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H547" s="4" t="inlineStr">
@@ -43212,7 +43227,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G548" s="4" t="n">
+      <c r="G548" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H548" s="4" t="inlineStr">
@@ -43289,7 +43304,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G549" s="4" t="n">
+      <c r="G549" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H549" s="4" t="inlineStr">
@@ -43366,7 +43381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G550" s="4" t="n">
+      <c r="G550" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H550" s="4" t="inlineStr">
@@ -43443,7 +43458,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G551" s="4" t="n">
+      <c r="G551" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H551" s="4" t="inlineStr">
@@ -43520,7 +43535,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G552" s="4" t="n">
+      <c r="G552" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H552" s="4" t="inlineStr">
@@ -43597,7 +43612,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G553" s="4" t="n">
+      <c r="G553" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H553" s="4" t="inlineStr">
@@ -43674,7 +43689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G554" s="4" t="n">
+      <c r="G554" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H554" s="4" t="inlineStr">
@@ -43751,7 +43766,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G555" s="4" t="n">
+      <c r="G555" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H555" s="4" t="inlineStr">
@@ -43828,7 +43843,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G556" s="4" t="n">
+      <c r="G556" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H556" s="4" t="inlineStr">
@@ -43905,7 +43920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G557" s="4" t="n">
+      <c r="G557" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H557" s="4" t="inlineStr">
@@ -43982,7 +43997,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G558" s="4" t="n">
+      <c r="G558" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H558" s="4" t="inlineStr">
@@ -44059,7 +44074,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G559" s="4" t="n">
+      <c r="G559" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H559" s="4" t="inlineStr">
@@ -44136,7 +44151,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G560" s="4" t="n">
+      <c r="G560" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H560" s="4" t="inlineStr">
@@ -44213,7 +44228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G561" s="4" t="n">
+      <c r="G561" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H561" s="4" t="inlineStr">
@@ -44290,7 +44305,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G562" s="4" t="n">
+      <c r="G562" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H562" s="4" t="inlineStr">
@@ -44367,7 +44382,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G563" s="4" t="n">
+      <c r="G563" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H563" s="4" t="inlineStr">
@@ -44444,7 +44459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G564" s="4" t="n">
+      <c r="G564" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H564" s="4" t="inlineStr">
@@ -44521,7 +44536,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G565" s="4" t="n">
+      <c r="G565" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H565" s="4" t="inlineStr">
@@ -44598,7 +44613,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G566" s="4" t="n">
+      <c r="G566" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H566" s="4" t="inlineStr">
@@ -44675,7 +44690,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G567" s="4" t="n">
+      <c r="G567" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H567" s="4" t="inlineStr">
@@ -44752,7 +44767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G568" s="4" t="n">
+      <c r="G568" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H568" s="4" t="inlineStr">
@@ -44785,7 +44800,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N568" s="4" t="n">
+      <c r="N568" s="8" t="n">
         <v>9.529999999999999</v>
       </c>
       <c r="O568" s="4" t="inlineStr">
@@ -44831,7 +44846,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G569" s="4" t="n">
+      <c r="G569" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H569" s="4" t="inlineStr">
@@ -44864,7 +44879,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N569" s="4" t="n">
+      <c r="N569" s="8" t="n">
         <v>8.167999999999999</v>
       </c>
       <c r="O569" s="4" t="inlineStr">
@@ -44910,7 +44925,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G570" s="4" t="n">
+      <c r="G570" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H570" s="4" t="inlineStr">
@@ -44943,7 +44958,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N570" s="4" t="n">
+      <c r="N570" s="8" t="n">
         <v>7.172</v>
       </c>
       <c r="O570" s="4" t="inlineStr">
@@ -44989,7 +45004,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G571" s="4" t="n">
+      <c r="G571" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H571" s="4" t="inlineStr">
@@ -45022,7 +45037,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N571" s="4" t="n">
+      <c r="N571" s="8" t="n">
         <v>7.948</v>
       </c>
       <c r="O571" s="4" t="inlineStr">
@@ -45068,7 +45083,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G572" s="4" t="n">
+      <c r="G572" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H572" s="4" t="inlineStr">
@@ -45101,7 +45116,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N572" s="4" t="n">
+      <c r="N572" s="8" t="n">
         <v>8.792999999999999</v>
       </c>
       <c r="O572" s="4" t="inlineStr">
@@ -45147,7 +45162,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G573" s="4" t="n">
+      <c r="G573" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H573" s="4" t="inlineStr">
@@ -45180,7 +45195,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N573" s="4" t="n">
+      <c r="N573" s="8" t="n">
         <v>10.177</v>
       </c>
       <c r="O573" s="4" t="inlineStr">
@@ -45226,7 +45241,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G574" s="4" t="n">
+      <c r="G574" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H574" s="4" t="inlineStr">
@@ -45259,7 +45274,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N574" s="4" t="n">
+      <c r="N574" s="8" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="O574" s="4" t="inlineStr">
@@ -45305,7 +45320,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G575" s="4" t="n">
+      <c r="G575" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H575" s="4" t="inlineStr">
@@ -45338,7 +45353,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N575" s="4" t="n">
+      <c r="N575" s="8" t="n">
         <v>9.808</v>
       </c>
       <c r="O575" s="4" t="inlineStr">
@@ -45384,7 +45399,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G576" s="4" t="n">
+      <c r="G576" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H576" s="4" t="inlineStr">
@@ -45417,7 +45432,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N576" s="4" t="n">
+      <c r="N576" s="8" t="n">
         <v>13.331</v>
       </c>
       <c r="O576" s="4" t="inlineStr">
@@ -45463,7 +45478,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G577" s="4" t="n">
+      <c r="G577" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H577" s="4" t="inlineStr">
@@ -45496,7 +45511,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N577" s="4" t="n">
+      <c r="N577" s="8" t="n">
         <v>13.616</v>
       </c>
       <c r="O577" s="4" t="inlineStr">
@@ -45542,7 +45557,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G578" s="4" t="n">
+      <c r="G578" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H578" s="4" t="inlineStr">
@@ -45575,7 +45590,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N578" s="4" t="n">
+      <c r="N578" s="8" t="n">
         <v>12.377</v>
       </c>
       <c r="O578" s="4" t="inlineStr">
@@ -45621,7 +45636,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G579" s="4" t="n">
+      <c r="G579" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H579" s="4" t="inlineStr">
@@ -45654,7 +45669,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N579" s="4" t="n">
+      <c r="N579" s="8" t="n">
         <v>14.487</v>
       </c>
       <c r="O579" s="4" t="inlineStr">
@@ -45700,7 +45715,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G580" s="4" t="n">
+      <c r="G580" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H580" s="4" t="inlineStr">
@@ -45733,7 +45748,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N580" s="4" t="n">
+      <c r="N580" s="8" t="n">
         <v>14.547</v>
       </c>
       <c r="O580" s="4" t="inlineStr">
@@ -45779,7 +45794,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G581" s="4" t="n">
+      <c r="G581" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H581" s="4" t="inlineStr">
@@ -45812,7 +45827,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N581" s="4" t="n">
+      <c r="N581" s="8" t="n">
         <v>13.304</v>
       </c>
       <c r="O581" s="4" t="inlineStr">
@@ -45858,7 +45873,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G582" s="4" t="n">
+      <c r="G582" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H582" s="4" t="inlineStr">
@@ -45891,7 +45906,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N582" s="4" t="n">
+      <c r="N582" s="8" t="n">
         <v>10.038</v>
       </c>
       <c r="O582" s="4" t="inlineStr">
@@ -45937,7 +45952,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G583" s="4" t="n">
+      <c r="G583" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H583" s="4" t="inlineStr">
@@ -45970,7 +45985,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N583" s="4" t="n">
+      <c r="N583" s="8" t="n">
         <v>8.109</v>
       </c>
       <c r="O583" s="4" t="inlineStr">
@@ -46016,7 +46031,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G584" s="4" t="n">
+      <c r="G584" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H584" s="4" t="inlineStr">
@@ -46049,7 +46064,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N584" s="4" t="n">
+      <c r="N584" s="8" t="n">
         <v>7.045</v>
       </c>
       <c r="O584" s="4" t="inlineStr">
@@ -46095,7 +46110,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G585" s="4" t="n">
+      <c r="G585" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H585" s="4" t="inlineStr">
@@ -46128,7 +46143,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N585" s="4" t="n">
+      <c r="N585" s="8" t="n">
         <v>6.262</v>
       </c>
       <c r="O585" s="4" t="inlineStr">
@@ -46174,7 +46189,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G586" s="4" t="n">
+      <c r="G586" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H586" s="4" t="inlineStr">
@@ -46207,7 +46222,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N586" s="4" t="n">
+      <c r="N586" s="8" t="n">
         <v>6.184</v>
       </c>
       <c r="O586" s="4" t="inlineStr">
@@ -46253,7 +46268,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G587" s="4" t="n">
+      <c r="G587" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H587" s="4" t="inlineStr">
@@ -46286,7 +46301,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N587" s="4" t="n">
+      <c r="N587" s="8" t="n">
         <v>7.216</v>
       </c>
       <c r="O587" s="4" t="inlineStr">
@@ -46332,7 +46347,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G588" s="4" t="n">
+      <c r="G588" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H588" s="4" t="inlineStr">
@@ -46365,7 +46380,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N588" s="4" t="n">
+      <c r="N588" s="8" t="n">
         <v>6.702</v>
       </c>
       <c r="O588" s="4" t="inlineStr">
@@ -46411,7 +46426,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G589" s="4" t="n">
+      <c r="G589" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H589" s="4" t="inlineStr">
@@ -46444,7 +46459,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N589" s="4" t="n">
+      <c r="N589" s="8" t="n">
         <v>6.264</v>
       </c>
       <c r="O589" s="4" t="inlineStr">
@@ -46490,7 +46505,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G590" s="4" t="n">
+      <c r="G590" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H590" s="4" t="inlineStr">
@@ -46523,7 +46538,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N590" s="4" t="n">
+      <c r="N590" s="8" t="n">
         <v>6.834</v>
       </c>
       <c r="O590" s="4" t="inlineStr">
@@ -46569,7 +46584,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G591" s="4" t="n">
+      <c r="G591" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H591" s="4" t="inlineStr">
@@ -46602,7 +46617,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N591" s="4" t="n">
+      <c r="N591" s="8" t="n">
         <v>6.32</v>
       </c>
       <c r="O591" s="4" t="inlineStr">
@@ -46648,7 +46663,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G592" s="4" t="n">
+      <c r="G592" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H592" s="4" t="inlineStr">
@@ -46681,7 +46696,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N592" s="4" t="n">
+      <c r="N592" s="8" t="n">
         <v>5.852</v>
       </c>
       <c r="O592" s="4" t="inlineStr">
@@ -46727,7 +46742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G593" s="4" t="n">
+      <c r="G593" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H593" s="4" t="inlineStr">
@@ -46760,7 +46775,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N593" s="4" t="n">
+      <c r="N593" s="8" t="n">
         <v>5.256</v>
       </c>
       <c r="O593" s="4" t="inlineStr">
@@ -46806,7 +46821,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G594" s="4" t="n">
+      <c r="G594" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H594" s="4" t="inlineStr">
@@ -46839,7 +46854,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N594" s="4" t="n">
+      <c r="N594" s="8" t="n">
         <v>4.518</v>
       </c>
       <c r="O594" s="4" t="inlineStr">
@@ -46885,7 +46900,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G595" s="4" t="n">
+      <c r="G595" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H595" s="4" t="inlineStr">
@@ -46918,7 +46933,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N595" s="4" t="n">
+      <c r="N595" s="8" t="n">
         <v>5.008</v>
       </c>
       <c r="O595" s="4" t="inlineStr">
@@ -46964,7 +46979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G596" s="4" t="n">
+      <c r="G596" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H596" s="4" t="inlineStr">
@@ -46997,7 +47012,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N596" s="4" t="n">
+      <c r="N596" s="8" t="n">
         <v>5.497</v>
       </c>
       <c r="O596" s="4" t="inlineStr">
@@ -47043,7 +47058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G597" s="4" t="n">
+      <c r="G597" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H597" s="4" t="inlineStr">
@@ -47076,7 +47091,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N597" s="4" t="n">
+      <c r="N597" s="8" t="n">
         <v>7.287</v>
       </c>
       <c r="O597" s="4" t="inlineStr">
@@ -47122,7 +47137,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G598" s="4" t="n">
+      <c r="G598" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H598" s="4" t="inlineStr">
@@ -47155,7 +47170,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N598" s="4" t="n">
+      <c r="N598" s="8" t="n">
         <v>6.693</v>
       </c>
       <c r="O598" s="4" t="inlineStr">
@@ -47201,7 +47216,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G599" s="4" t="n">
+      <c r="G599" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H599" s="4" t="inlineStr">
@@ -47234,7 +47249,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N599" s="4" t="n">
+      <c r="N599" s="8" t="n">
         <v>5.352</v>
       </c>
       <c r="O599" s="4" t="inlineStr">
@@ -47280,7 +47295,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G600" s="4" t="n">
+      <c r="G600" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H600" s="4" t="inlineStr">
@@ -47313,7 +47328,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N600" s="4" t="n">
+      <c r="N600" s="8" t="n">
         <v>5.108</v>
       </c>
       <c r="O600" s="4" t="inlineStr">
@@ -47359,7 +47374,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G601" s="4" t="n">
+      <c r="G601" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H601" s="4" t="inlineStr">
@@ -47392,7 +47407,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N601" s="4" t="n">
+      <c r="N601" s="8" t="n">
         <v>5.017</v>
       </c>
       <c r="O601" s="4" t="inlineStr">
@@ -47438,7 +47453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G602" s="4" t="n">
+      <c r="G602" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H602" s="4" t="inlineStr">
@@ -47471,7 +47486,7 @@
           <t>Tasa de desempleo masculina</t>
         </is>
       </c>
-      <c r="N602" s="4" t="n">
+      <c r="N602" s="8" t="n">
         <v>5.001</v>
       </c>
       <c r="O602" s="4" t="inlineStr">
@@ -47517,7 +47532,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G603" s="4" t="n">
+      <c r="G603" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H603" s="4" t="inlineStr">
@@ -47594,7 +47609,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G604" s="4" t="n">
+      <c r="G604" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H604" s="4" t="inlineStr">
@@ -47671,7 +47686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G605" s="4" t="n">
+      <c r="G605" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H605" s="4" t="inlineStr">
@@ -47748,7 +47763,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G606" s="4" t="n">
+      <c r="G606" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H606" s="4" t="inlineStr">
@@ -47825,7 +47840,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G607" s="4" t="n">
+      <c r="G607" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H607" s="4" t="inlineStr">
@@ -47902,7 +47917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G608" s="4" t="n">
+      <c r="G608" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H608" s="4" t="inlineStr">
@@ -47979,7 +47994,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G609" s="4" t="n">
+      <c r="G609" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H609" s="4" t="inlineStr">
@@ -48056,7 +48071,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G610" s="4" t="n">
+      <c r="G610" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H610" s="4" t="inlineStr">
@@ -48133,7 +48148,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G611" s="4" t="n">
+      <c r="G611" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H611" s="4" t="inlineStr">
@@ -48210,7 +48225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G612" s="4" t="n">
+      <c r="G612" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H612" s="4" t="inlineStr">
@@ -48287,7 +48302,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G613" s="4" t="n">
+      <c r="G613" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H613" s="4" t="inlineStr">
@@ -48364,7 +48379,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G614" s="4" t="n">
+      <c r="G614" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H614" s="4" t="inlineStr">
@@ -48441,7 +48456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G615" s="4" t="n">
+      <c r="G615" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H615" s="4" t="inlineStr">
@@ -48518,7 +48533,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G616" s="4" t="n">
+      <c r="G616" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H616" s="4" t="inlineStr">
@@ -48595,7 +48610,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G617" s="4" t="n">
+      <c r="G617" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H617" s="4" t="inlineStr">
@@ -48672,7 +48687,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G618" s="4" t="n">
+      <c r="G618" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H618" s="4" t="inlineStr">
@@ -48749,7 +48764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G619" s="4" t="n">
+      <c r="G619" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H619" s="4" t="inlineStr">
@@ -48826,7 +48841,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G620" s="4" t="n">
+      <c r="G620" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H620" s="4" t="inlineStr">
@@ -48903,7 +48918,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G621" s="4" t="n">
+      <c r="G621" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H621" s="4" t="inlineStr">
@@ -48980,7 +48995,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G622" s="4" t="n">
+      <c r="G622" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H622" s="4" t="inlineStr">
@@ -49057,7 +49072,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G623" s="4" t="n">
+      <c r="G623" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H623" s="4" t="inlineStr">
@@ -49134,7 +49149,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G624" s="4" t="n">
+      <c r="G624" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H624" s="4" t="inlineStr">
@@ -49211,7 +49226,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G625" s="4" t="n">
+      <c r="G625" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H625" s="4" t="inlineStr">
@@ -49288,7 +49303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G626" s="4" t="n">
+      <c r="G626" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H626" s="4" t="inlineStr">
@@ -49365,7 +49380,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G627" s="4" t="n">
+      <c r="G627" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H627" s="4" t="inlineStr">
@@ -49442,7 +49457,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G628" s="4" t="n">
+      <c r="G628" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H628" s="4" t="inlineStr">
@@ -49519,7 +49534,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G629" s="4" t="n">
+      <c r="G629" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H629" s="4" t="inlineStr">
@@ -49596,7 +49611,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G630" s="4" t="n">
+      <c r="G630" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H630" s="4" t="inlineStr">
@@ -49673,7 +49688,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G631" s="4" t="n">
+      <c r="G631" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H631" s="4" t="inlineStr">
@@ -49750,7 +49765,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G632" s="4" t="n">
+      <c r="G632" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H632" s="4" t="inlineStr">
@@ -49827,7 +49842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G633" s="4" t="n">
+      <c r="G633" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H633" s="4" t="inlineStr">
@@ -49904,7 +49919,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G634" s="4" t="n">
+      <c r="G634" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H634" s="4" t="inlineStr">
@@ -49937,7 +49952,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N634" s="4" t="n">
+      <c r="N634" s="8" t="n">
         <v>9.449999999999999</v>
       </c>
       <c r="O634" s="4" t="inlineStr">
@@ -49983,7 +49998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G635" s="4" t="n">
+      <c r="G635" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H635" s="4" t="inlineStr">
@@ -50016,7 +50031,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N635" s="4" t="n">
+      <c r="N635" s="8" t="n">
         <v>7.69</v>
       </c>
       <c r="O635" s="4" t="inlineStr">
@@ -50062,7 +50077,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G636" s="4" t="n">
+      <c r="G636" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H636" s="4" t="inlineStr">
@@ -50095,7 +50110,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N636" s="4" t="n">
+      <c r="N636" s="8" t="n">
         <v>6.6</v>
       </c>
       <c r="O636" s="4" t="inlineStr">
@@ -50141,7 +50156,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G637" s="4" t="n">
+      <c r="G637" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H637" s="4" t="inlineStr">
@@ -50174,7 +50189,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N637" s="4" t="n">
+      <c r="N637" s="8" t="n">
         <v>8.56</v>
       </c>
       <c r="O637" s="4" t="inlineStr">
@@ -50220,7 +50235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G638" s="4" t="n">
+      <c r="G638" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H638" s="4" t="inlineStr">
@@ -50253,7 +50268,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N638" s="4" t="n">
+      <c r="N638" s="8" t="n">
         <v>10.24</v>
       </c>
       <c r="O638" s="4" t="inlineStr">
@@ -50299,7 +50314,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G639" s="4" t="n">
+      <c r="G639" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H639" s="4" t="inlineStr">
@@ -50332,7 +50347,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N639" s="4" t="n">
+      <c r="N639" s="8" t="n">
         <v>11.77</v>
       </c>
       <c r="O639" s="4" t="inlineStr">
@@ -50378,7 +50393,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G640" s="4" t="n">
+      <c r="G640" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H640" s="4" t="inlineStr">
@@ -50411,7 +50426,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N640" s="4" t="n">
+      <c r="N640" s="8" t="n">
         <v>11.16</v>
       </c>
       <c r="O640" s="4" t="inlineStr">
@@ -50457,7 +50472,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G641" s="4" t="n">
+      <c r="G641" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H641" s="4" t="inlineStr">
@@ -50490,7 +50505,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N641" s="4" t="n">
+      <c r="N641" s="8" t="n">
         <v>11.15</v>
       </c>
       <c r="O641" s="4" t="inlineStr">
@@ -50536,7 +50551,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G642" s="4" t="n">
+      <c r="G642" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H642" s="4" t="inlineStr">
@@ -50569,7 +50584,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N642" s="4" t="n">
+      <c r="N642" s="8" t="n">
         <v>14.53</v>
       </c>
       <c r="O642" s="4" t="inlineStr">
@@ -50615,7 +50630,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G643" s="4" t="n">
+      <c r="G643" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H643" s="4" t="inlineStr">
@@ -50648,7 +50663,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N643" s="4" t="n">
+      <c r="N643" s="8" t="n">
         <v>13.99</v>
       </c>
       <c r="O643" s="4" t="inlineStr">
@@ -50694,7 +50709,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G644" s="4" t="n">
+      <c r="G644" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H644" s="4" t="inlineStr">
@@ -50727,7 +50742,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N644" s="4" t="n">
+      <c r="N644" s="8" t="n">
         <v>13.04</v>
       </c>
       <c r="O644" s="4" t="inlineStr">
@@ -50773,7 +50788,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G645" s="4" t="n">
+      <c r="G645" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H645" s="4" t="inlineStr">
@@ -50806,7 +50821,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N645" s="4" t="n">
+      <c r="N645" s="8" t="n">
         <v>16.17</v>
       </c>
       <c r="O645" s="4" t="inlineStr">
@@ -50852,7 +50867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G646" s="4" t="n">
+      <c r="G646" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H646" s="4" t="inlineStr">
@@ -50885,7 +50900,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N646" s="4" t="n">
+      <c r="N646" s="8" t="n">
         <v>16.78</v>
       </c>
       <c r="O646" s="4" t="inlineStr">
@@ -50931,7 +50946,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G647" s="4" t="n">
+      <c r="G647" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H647" s="4" t="inlineStr">
@@ -50964,7 +50979,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N647" s="4" t="n">
+      <c r="N647" s="8" t="n">
         <v>15.07</v>
       </c>
       <c r="O647" s="4" t="inlineStr">
@@ -51010,7 +51025,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G648" s="4" t="n">
+      <c r="G648" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H648" s="4" t="inlineStr">
@@ -51043,7 +51058,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N648" s="4" t="n">
+      <c r="N648" s="8" t="n">
         <v>10.663</v>
       </c>
       <c r="O648" s="4" t="inlineStr">
@@ -51089,7 +51104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G649" s="4" t="n">
+      <c r="G649" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H649" s="4" t="inlineStr">
@@ -51122,7 +51137,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N649" s="4" t="n">
+      <c r="N649" s="8" t="n">
         <v>8.606</v>
       </c>
       <c r="O649" s="4" t="inlineStr">
@@ -51168,7 +51183,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G650" s="4" t="n">
+      <c r="G650" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H650" s="4" t="inlineStr">
@@ -51201,7 +51216,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N650" s="4" t="n">
+      <c r="N650" s="8" t="n">
         <v>7.279</v>
       </c>
       <c r="O650" s="4" t="inlineStr">
@@ -51247,7 +51262,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G651" s="4" t="n">
+      <c r="G651" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H651" s="4" t="inlineStr">
@@ -51280,7 +51295,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N651" s="4" t="n">
+      <c r="N651" s="8" t="n">
         <v>6.245</v>
       </c>
       <c r="O651" s="4" t="inlineStr">
@@ -51326,7 +51341,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G652" s="4" t="n">
+      <c r="G652" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H652" s="4" t="inlineStr">
@@ -51359,7 +51374,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N652" s="4" t="n">
+      <c r="N652" s="8" t="n">
         <v>6.097</v>
       </c>
       <c r="O652" s="4" t="inlineStr">
@@ -51405,7 +51420,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G653" s="4" t="n">
+      <c r="G653" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H653" s="4" t="inlineStr">
@@ -51438,7 +51453,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N653" s="4" t="n">
+      <c r="N653" s="8" t="n">
         <v>7.112</v>
       </c>
       <c r="O653" s="4" t="inlineStr">
@@ -51484,7 +51499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G654" s="4" t="n">
+      <c r="G654" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H654" s="4" t="inlineStr">
@@ -51517,7 +51532,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N654" s="4" t="n">
+      <c r="N654" s="8" t="n">
         <v>6.902</v>
       </c>
       <c r="O654" s="4" t="inlineStr">
@@ -51563,7 +51578,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G655" s="4" t="n">
+      <c r="G655" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H655" s="4" t="inlineStr">
@@ -51596,7 +51611,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N655" s="4" t="n">
+      <c r="N655" s="8" t="n">
         <v>6.601</v>
       </c>
       <c r="O655" s="4" t="inlineStr">
@@ -51642,7 +51657,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G656" s="4" t="n">
+      <c r="G656" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H656" s="4" t="inlineStr">
@@ -51675,7 +51690,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N656" s="4" t="n">
+      <c r="N656" s="8" t="n">
         <v>7.54</v>
       </c>
       <c r="O656" s="4" t="inlineStr">
@@ -51721,7 +51736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G657" s="4" t="n">
+      <c r="G657" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H657" s="4" t="inlineStr">
@@ -51754,7 +51769,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N657" s="4" t="n">
+      <c r="N657" s="8" t="n">
         <v>6.821</v>
       </c>
       <c r="O657" s="4" t="inlineStr">
@@ -51800,7 +51815,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G658" s="4" t="n">
+      <c r="G658" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H658" s="4" t="inlineStr">
@@ -51833,7 +51848,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N658" s="4" t="n">
+      <c r="N658" s="8" t="n">
         <v>6.139</v>
       </c>
       <c r="O658" s="4" t="inlineStr">
@@ -51879,7 +51894,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G659" s="4" t="n">
+      <c r="G659" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H659" s="4" t="inlineStr">
@@ -51912,7 +51927,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N659" s="4" t="n">
+      <c r="N659" s="8" t="n">
         <v>5.319</v>
       </c>
       <c r="O659" s="4" t="inlineStr">
@@ -51958,7 +51973,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G660" s="4" t="n">
+      <c r="G660" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H660" s="4" t="inlineStr">
@@ -51991,7 +52006,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N660" s="4" t="n">
+      <c r="N660" s="8" t="n">
         <v>5.045</v>
       </c>
       <c r="O660" s="4" t="inlineStr">
@@ -52037,7 +52052,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G661" s="4" t="n">
+      <c r="G661" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H661" s="4" t="inlineStr">
@@ -52070,7 +52085,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N661" s="4" t="n">
+      <c r="N661" s="8" t="n">
         <v>5.468</v>
       </c>
       <c r="O661" s="4" t="inlineStr">
@@ -52116,7 +52131,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G662" s="4" t="n">
+      <c r="G662" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H662" s="4" t="inlineStr">
@@ -52149,7 +52164,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N662" s="4" t="n">
+      <c r="N662" s="8" t="n">
         <v>5.89</v>
       </c>
       <c r="O662" s="4" t="inlineStr">
@@ -52195,7 +52210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G663" s="4" t="n">
+      <c r="G663" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H663" s="4" t="inlineStr">
@@ -52228,7 +52243,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N663" s="4" t="n">
+      <c r="N663" s="8" t="n">
         <v>7.53</v>
       </c>
       <c r="O663" s="4" t="inlineStr">
@@ -52274,7 +52289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G664" s="4" t="n">
+      <c r="G664" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H664" s="4" t="inlineStr">
@@ -52307,7 +52322,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N664" s="4" t="n">
+      <c r="N664" s="8" t="n">
         <v>7.027</v>
       </c>
       <c r="O664" s="4" t="inlineStr">
@@ -52353,7 +52368,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G665" s="4" t="n">
+      <c r="G665" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H665" s="4" t="inlineStr">
@@ -52386,7 +52401,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N665" s="4" t="n">
+      <c r="N665" s="8" t="n">
         <v>5.646</v>
       </c>
       <c r="O665" s="4" t="inlineStr">
@@ -52432,7 +52447,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G666" s="4" t="n">
+      <c r="G666" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H666" s="4" t="inlineStr">
@@ -52465,7 +52480,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N666" s="4" t="n">
+      <c r="N666" s="8" t="n">
         <v>5.407</v>
       </c>
       <c r="O666" s="4" t="inlineStr">
@@ -52511,7 +52526,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G667" s="4" t="n">
+      <c r="G667" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H667" s="4" t="inlineStr">
@@ -52544,7 +52559,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N667" s="4" t="n">
+      <c r="N667" s="8" t="n">
         <v>5.321</v>
       </c>
       <c r="O667" s="4" t="inlineStr">
@@ -52590,7 +52605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G668" s="4" t="n">
+      <c r="G668" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H668" s="4" t="inlineStr">
@@ -52623,7 +52638,7 @@
           <t>Tasa de desempleo total</t>
         </is>
       </c>
-      <c r="N668" s="4" t="n">
+      <c r="N668" s="8" t="n">
         <v>5.307</v>
       </c>
       <c r="O668" s="4" t="inlineStr">
@@ -52728,7 +52743,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -52738,7 +52753,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>662</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_mercado_laboral.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17095,7 +17095,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18481,7 +18481,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21323,7 +21323,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22324,7 +22324,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22786,7 +22786,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22940,7 +22940,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23479,7 +23479,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23793,7 +23793,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24504,7 +24504,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25057,7 +25057,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25215,7 +25215,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25294,7 +25294,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26400,7 +26400,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26554,7 +26554,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26862,7 +26862,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27247,7 +27247,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27478,7 +27478,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27940,7 +27940,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28171,7 +28171,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28248,7 +28248,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28633,7 +28633,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29342,7 +29342,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29500,7 +29500,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30211,7 +30211,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30369,7 +30369,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30843,7 +30843,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30922,7 +30922,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31159,7 +31159,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31317,7 +31317,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31396,7 +31396,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31785,7 +31785,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33248,7 +33248,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34338,7 +34338,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34654,7 +34654,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34812,7 +34812,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35286,7 +35286,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35602,7 +35602,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35681,7 +35681,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35918,7 +35918,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36076,7 +36076,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36234,7 +36234,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36392,7 +36392,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36629,7 +36629,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36862,7 +36862,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36939,7 +36939,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37016,7 +37016,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37093,7 +37093,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37170,7 +37170,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37247,7 +37247,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37478,7 +37478,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37709,7 +37709,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37786,7 +37786,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38017,7 +38017,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38479,7 +38479,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38633,7 +38633,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38710,7 +38710,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38787,7 +38787,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -38941,7 +38941,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39018,7 +39018,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39095,7 +39095,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39253,7 +39253,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39332,7 +39332,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39411,7 +39411,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39490,7 +39490,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39727,7 +39727,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39885,7 +39885,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -39964,7 +39964,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40043,7 +40043,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40359,7 +40359,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40438,7 +40438,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40833,7 +40833,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -40912,7 +40912,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -40991,7 +40991,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41070,7 +41070,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41307,7 +41307,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41465,7 +41465,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41623,7 +41623,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41702,7 +41702,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -41937,7 +41937,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42091,7 +42091,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42168,7 +42168,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42476,7 +42476,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42861,7 +42861,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -42938,7 +42938,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43015,7 +43015,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43400,7 +43400,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43554,7 +43554,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43708,7 +43708,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -43939,7 +43939,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44016,7 +44016,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44170,7 +44170,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44405,7 +44405,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44563,7 +44563,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44642,7 +44642,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45037,7 +45037,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45195,7 +45195,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45274,7 +45274,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45432,7 +45432,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45511,7 +45511,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45590,7 +45590,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -45906,7 +45906,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -45985,7 +45985,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46064,7 +46064,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46301,7 +46301,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46459,7 +46459,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46538,7 +46538,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46696,7 +46696,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -46854,7 +46854,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47012,7 +47012,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47089,7 +47089,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47166,7 +47166,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47320,7 +47320,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47397,7 +47397,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47551,7 +47551,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -47705,7 +47705,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -47782,7 +47782,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -47859,7 +47859,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -47936,7 +47936,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48013,7 +48013,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48167,7 +48167,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48398,7 +48398,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -48629,7 +48629,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -48937,7 +48937,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49091,7 +49091,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49322,7 +49322,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49399,7 +49399,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49478,7 +49478,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -49557,7 +49557,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -49636,7 +49636,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -49794,7 +49794,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -49952,7 +49952,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50031,7 +50031,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50189,7 +50189,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50268,7 +50268,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50505,7 +50505,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -50584,7 +50584,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -50742,7 +50742,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -50900,7 +50900,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51058,7 +51058,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51216,7 +51216,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -51690,7 +51690,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -51848,7 +51848,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -51927,7 +51927,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52006,7 +52006,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52085,7 +52085,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52164,7 +52164,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52249,7 +52249,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
